--- a/AAII_Financials/Quarterly/IOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IOT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,239 +656,252 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45227</v>
+      </c>
+      <c r="E7" s="2">
         <v>45136</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45045</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44954</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44863</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44772</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44590</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44499</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44317</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44226</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44044</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43953</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>237500</v>
+      </c>
+      <c r="E8" s="3">
         <v>219300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>204300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>186600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>169800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>153500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>142600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>125800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>113800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>101000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>87700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>75900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>66200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>56800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>51000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>61600</v>
+      </c>
+      <c r="E9" s="3">
         <v>58900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>57600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>51500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>47300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>44300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>39600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>38700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>31800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>28400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>25600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>21200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>175900</v>
+      </c>
+      <c r="E10" s="3">
         <v>160400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>146700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>135100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>122500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>109200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>103000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>87100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>82000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>72600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>62100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>54700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>47500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>37900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>34400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -907,58 +920,62 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>60800</v>
+      </c>
+      <c r="E12" s="3">
         <v>64000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>60400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>54600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>50000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>41800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>41000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>126500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>29700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>25500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>23500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>20200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>33500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>21900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>24200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1007,13 +1024,16 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1028,17 +1048,17 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>1100</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>1500</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1049,16 +1069,19 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>6800</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1107,8 +1130,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1124,108 +1150,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>292300</v>
+      </c>
+      <c r="E17" s="3">
         <v>289000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>280100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>246600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>233300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>219300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>212900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>377500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>146100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>132300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>126300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>111200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>120500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>112900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>114700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>109900</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-54800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-69700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-75800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-60000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-63500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-65800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-70300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-251700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-32300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-31300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-38600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-35300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-54300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-56100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-63700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-68300</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1244,108 +1277,115 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E20" s="3">
         <v>10200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>8900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1600</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-800</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3">
         <v>100</v>
       </c>
       <c r="R20" s="3">
+        <v>100</v>
+      </c>
+      <c r="S20" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-41700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-55800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-63400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-48000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-54500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-61600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-67900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-249800</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O21" s="3">
         <v>-25400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-46000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1394,91 +1434,97 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-45400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-59500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-66900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-51500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-57900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-64200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-70300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-252000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-32400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-31000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-38400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-36200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-54300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-63600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>700</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>800</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1492,10 +1538,13 @@
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1544,108 +1593,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-60000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-67900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-53600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-58600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-64300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-71000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-252800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-32400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-31400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-38400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-36200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-54300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-63700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-60000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-67900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-53600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-58600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-64300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-71000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-252800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-32400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-31400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-38400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-36200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-54300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-63700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1694,8 +1752,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1744,8 +1805,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1794,8 +1858,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1844,108 +1911,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-8900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1600</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>800</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
       </c>
       <c r="R32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S32" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-60000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-67900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-53600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-58600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-64300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-71000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-252800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-32400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-38400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-36200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-54300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-63700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1994,113 +2070,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-60000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-67900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-53600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-58600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-64300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-71000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-252800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-32400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-38400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-36200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-54300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-63700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45227</v>
+      </c>
+      <c r="E38" s="2">
         <v>45136</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45045</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44954</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44863</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44772</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44590</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44499</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44317</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44226</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44044</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43953</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2119,8 +2204,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2139,38 +2225,39 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>208100</v>
+      </c>
+      <c r="E41" s="3">
         <v>196000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>192100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>200700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>447000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>826100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>859800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>921200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>267500</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2189,26 +2276,29 @@
       <c r="R41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>451700</v>
+      </c>
+      <c r="E42" s="3">
         <v>528800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>533900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>489200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>291800</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I42" s="3" t="s">
         <v>16</v>
       </c>
@@ -2224,8 +2314,8 @@
       <c r="M42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2239,38 +2329,41 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>115200</v>
+      </c>
+      <c r="E43" s="3">
         <v>115400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>102600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>122900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>90800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>77400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>84900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>82000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>59400</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2289,38 +2382,41 @@
       <c r="R43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E44" s="3">
         <v>21800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>32400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>40600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>44500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>39100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>42000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>33100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>22300</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>16</v>
       </c>
@@ -2339,38 +2435,41 @@
       <c r="R44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>138800</v>
+      </c>
+      <c r="E45" s="3">
         <v>116000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>109600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>104200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>88900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>93400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>81900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>63900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>56800</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2389,38 +2488,41 @@
       <c r="R45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>940900</v>
+      </c>
+      <c r="E46" s="3">
         <v>978000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>970600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>957500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>963000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1036000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1068600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1100200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>406000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>16</v>
       </c>
@@ -2439,26 +2541,29 @@
       <c r="R46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>189400</v>
+      </c>
+      <c r="E47" s="3">
         <v>109700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>87800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>113100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>63700</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>16</v>
       </c>
@@ -2474,8 +2579,8 @@
       <c r="M47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -2489,38 +2594,41 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>142100</v>
+      </c>
+      <c r="E48" s="3">
         <v>151100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>156100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>171900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>175900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>180100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>179200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>171200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>168800</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>16</v>
       </c>
@@ -2539,8 +2647,11 @@
       <c r="R48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2589,8 +2700,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2639,8 +2753,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2689,38 +2806,41 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>414000</v>
+      </c>
+      <c r="E52" s="3">
         <v>403900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>384100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>374500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>347400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>312900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>297100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>296600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>264700</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>16</v>
       </c>
@@ -2739,8 +2859,11 @@
       <c r="R52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2789,38 +2912,41 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1686400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1642600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1598500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1617000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1550000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1529000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1545000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1567900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>839500</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>16</v>
       </c>
@@ -2839,8 +2965,11 @@
       <c r="R54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2859,8 +2988,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2879,38 +3009,39 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E57" s="3">
         <v>34700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>29200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>30100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>43400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>20400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>40800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>54700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>42300</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>16</v>
       </c>
@@ -2929,8 +3060,11 @@
       <c r="R57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2979,38 +3113,41 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>468200</v>
+      </c>
+      <c r="E59" s="3">
         <v>444700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>411600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>412000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>334500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>321400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>311500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>283600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>242100</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3029,38 +3166,41 @@
       <c r="R59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>506500</v>
+      </c>
+      <c r="E60" s="3">
         <v>479300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>440900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>442200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>377800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>341800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>352300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>338300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>284400</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3079,8 +3219,11 @@
       <c r="R60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3129,38 +3272,41 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>229000</v>
+      </c>
+      <c r="E62" s="3">
         <v>226900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>235100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>236800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>232400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>234100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>230300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>240700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>235300</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>16</v>
       </c>
@@ -3179,8 +3325,11 @@
       <c r="R62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3229,8 +3378,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3279,8 +3431,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3329,38 +3484,41 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>735400</v>
+      </c>
+      <c r="E66" s="3">
         <v>706300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>676000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>679000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>610200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>575900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>582500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>579000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>519700</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>16</v>
       </c>
@@ -3379,8 +3537,11 @@
       <c r="R66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3399,8 +3560,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3449,8 +3611,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3499,8 +3664,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3526,11 +3694,11 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>949100</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -3549,8 +3717,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3599,38 +3770,41 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1341700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1296200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1236200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1168400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1114800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1056200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-991900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-921000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-668200</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>16</v>
       </c>
@@ -3649,8 +3823,11 @@
       <c r="R72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3699,8 +3876,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3749,8 +3929,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3799,38 +3982,41 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>950900</v>
+      </c>
+      <c r="E76" s="3">
         <v>936400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>922600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>938000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>939800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>953100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>962400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>988900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-629200</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>16</v>
       </c>
@@ -3849,8 +4035,11 @@
       <c r="R76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3899,113 +4088,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45227</v>
+      </c>
+      <c r="E80" s="2">
         <v>45136</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45045</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44954</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44863</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44772</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44590</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44499</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44317</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44226</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44044</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43953</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-60000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-67900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-53600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-58600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-64300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-71000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-252800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-32400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-38400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-36200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-54300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-63700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4024,35 +4222,36 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E83" s="3">
         <v>3700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2200</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>16</v>
       </c>
@@ -4068,14 +4267,17 @@
       <c r="P83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4124,8 +4326,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4174,8 +4379,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4224,8 +4432,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4274,8 +4485,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4324,35 +4538,38 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E89" s="3">
         <v>7700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-12900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-37000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-48800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-48300</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>16</v>
       </c>
@@ -4368,14 +4585,17 @@
       <c r="P89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
+      <c r="Q89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4394,40 +4614,41 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9400</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>16</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>16</v>
@@ -4438,14 +4659,17 @@
       <c r="P91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4494,8 +4718,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4544,35 +4771,38 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-16900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-249300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-365600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9500</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>16</v>
       </c>
@@ -4588,14 +4818,17 @@
       <c r="P94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4614,8 +4847,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4664,8 +4898,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4714,8 +4951,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4764,8 +5004,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4814,35 +5057,38 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
         <v>12500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>9700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>703000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>16</v>
       </c>
@@ -4858,31 +5104,34 @@
       <c r="P100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-200</v>
       </c>
       <c r="I101" s="3">
         <v>-200</v>
@@ -4890,8 +5139,8 @@
       <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>16</v>
+      <c r="K101" s="3">
+        <v>-200</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>16</v>
@@ -4908,41 +5157,44 @@
       <c r="P101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E102" s="3">
         <v>3800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-246400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-379100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-33700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-61400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>645100</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>16</v>
       </c>
@@ -4958,10 +5210,13 @@
       <c r="P102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
+      <c r="Q102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
   <si>
     <t>IOT</t>
   </si>
@@ -656,252 +656,277 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45416</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45325</v>
+      </c>
+      <c r="F7" s="2">
         <v>45227</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45136</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45045</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44954</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44863</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44772</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44590</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44499</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44317</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44226</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44044</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43953</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>280700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>276300</v>
+      </c>
+      <c r="F8" s="3">
         <v>237500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>219300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>204300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>186600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>169800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>153500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>142600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>125800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>113800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>101000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>87700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>75900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>66200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>56800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>51000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>68600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>69000</v>
+      </c>
+      <c r="F9" s="3">
         <v>61600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>58900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>57600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>51500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>47300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>44300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>39600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>38700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>31800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>28400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>25600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>21200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>18700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>18900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>16600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>212100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>207300</v>
+      </c>
+      <c r="F10" s="3">
         <v>175900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>160400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>146700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>135100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>122500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>109200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>103000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>87100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>82000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>72600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>62100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>54700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>47500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>37900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>34400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -921,61 +946,69 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>73400</v>
+      </c>
+      <c r="F12" s="3">
         <v>60800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>64000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>60400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>54600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>50000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>41800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>41000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>126500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>29700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>25500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>23500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>20200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>33500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>21900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>24200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1027,20 +1060,26 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="3">
+        <v>68700</v>
+      </c>
+      <c r="F14" s="3">
         <v>4800</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
@@ -1051,20 +1090,20 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>1100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>1500</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1072,16 +1111,22 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>6800</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1133,8 +1178,14 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1151,114 +1202,128 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>346700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>399300</v>
+      </c>
+      <c r="F17" s="3">
         <v>292300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>289000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>280100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>246600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>233300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>219300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>212900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>377500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>146100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>132300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>126300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>111200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>120500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>112900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>114700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>109900</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-54800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-69700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-75800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-60000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-63500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-65800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-70300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-251700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-32300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-31300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-38600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-35300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-54300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-56100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-63700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-68300</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1278,114 +1343,128 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F20" s="3">
         <v>9400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>10200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>8900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>8500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>5600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>1600</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-800</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-51500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-106800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-41700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-55800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-63400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-48000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-54500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-61600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-67900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-249800</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-25400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-46000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1437,100 +1516,112 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-55900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-111500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-45400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-59500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-66900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-51500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-57900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-64200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-70300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-252000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-32400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-31000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-38400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-36200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-54300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-56000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-63600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>2100</v>
-      </c>
-      <c r="H24" s="3">
-        <v>700</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
       </c>
       <c r="J24" s="3">
         <v>700</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>700</v>
+      </c>
+      <c r="M24" s="3">
         <v>800</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -1541,10 +1632,16 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1596,114 +1693,132 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-56300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-113400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-45500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-60000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-67900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-53600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-58600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-64300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-71000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-252800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-32400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-31400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-38400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-36200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-54300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-56000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-63700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-56300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-113400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-45500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-60000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-67900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-53600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-58600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-64300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-71000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-252800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-32400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-31400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-38400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-36200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-54300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-56000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-63700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1755,8 +1870,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1808,8 +1929,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1861,8 +1988,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1914,114 +2047,132 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-9400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-10200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-8900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-8500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-5600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-1600</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>800</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-56300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-113400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-45500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-60000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-67900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-53600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-58600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-64300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-71000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-252800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-32400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-31400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-38400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-36200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-54300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-56000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-63700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2073,119 +2224,137 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-56300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-113400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-45500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-60000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-67900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-53600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-58600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-64300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-71000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-252800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-32400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-31400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-38400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-36200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-54300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-56000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-63700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45416</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45325</v>
+      </c>
+      <c r="F38" s="2">
         <v>45227</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45136</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45045</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44954</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44863</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44772</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44590</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44499</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44317</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44226</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44044</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43953</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2205,8 +2374,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2226,44 +2397,46 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>162500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>135500</v>
+      </c>
+      <c r="F41" s="3">
         <v>208100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>196000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>192100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>200700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>447000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>826100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>859800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>921200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>267500</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2279,32 +2452,38 @@
       <c r="S41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>431900</v>
+      </c>
+      <c r="E42" s="3">
+        <v>412100</v>
+      </c>
+      <c r="F42" s="3">
         <v>451700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>528800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>533900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>489200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>291800</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>16</v>
       </c>
@@ -2317,11 +2496,11 @@
       <c r="N42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -2332,44 +2511,50 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>143800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>161800</v>
+      </c>
+      <c r="F43" s="3">
         <v>115200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>115400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>102600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>122900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>90800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>77400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>84900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>82000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>59400</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2385,44 +2570,50 @@
       <c r="S43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>22200</v>
+      </c>
+      <c r="F44" s="3">
         <v>27100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>21800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>32400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>40600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>44500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>39100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>42000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>33100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>22300</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>16</v>
       </c>
@@ -2438,44 +2629,50 @@
       <c r="S44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>155100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>155200</v>
+      </c>
+      <c r="F45" s="3">
         <v>138800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>116000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>109600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>104200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>88900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>93400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>81900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>63900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>56800</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2491,44 +2688,50 @@
       <c r="S45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>923700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>887000</v>
+      </c>
+      <c r="F46" s="3">
         <v>940900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>978000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>970600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>957500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>963000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1036000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1068600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1100200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>406000</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>16</v>
       </c>
@@ -2544,32 +2747,38 @@
       <c r="S46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>250600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>276200</v>
+      </c>
+      <c r="F47" s="3">
         <v>189400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>109700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>87800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>113100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>63700</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>16</v>
       </c>
@@ -2582,11 +2791,11 @@
       <c r="N47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2597,44 +2806,50 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>133300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>136900</v>
+      </c>
+      <c r="F48" s="3">
         <v>142100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>151100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>156100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>171900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>175900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>180100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>179200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>171200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>168800</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>16</v>
       </c>
@@ -2650,8 +2865,14 @@
       <c r="S48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2703,8 +2924,14 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2756,8 +2983,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2809,44 +3042,50 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>441800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>434800</v>
+      </c>
+      <c r="F52" s="3">
         <v>414000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>403900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>384100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>374500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>347400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>312900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>297100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>296600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>264700</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>16</v>
       </c>
@@ -2862,8 +3101,14 @@
       <c r="S52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2915,44 +3160,50 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1749400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1734800</v>
+      </c>
+      <c r="F54" s="3">
         <v>1686400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1642600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1598500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1617000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1550000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1529000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1545000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1567900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>839500</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>16</v>
       </c>
@@ -2968,8 +3219,14 @@
       <c r="S54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2989,8 +3246,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3010,44 +3269,46 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>46300</v>
+      </c>
+      <c r="F57" s="3">
         <v>38300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>34700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>29200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>30100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>43400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>20400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>40800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>54700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>42300</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3063,8 +3324,14 @@
       <c r="S57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3116,44 +3383,50 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>560100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>545500</v>
+      </c>
+      <c r="F59" s="3">
         <v>468200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>444700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>411600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>412000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>334500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>321400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>311500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>283600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>242100</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3169,44 +3442,50 @@
       <c r="S59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>601300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>591800</v>
+      </c>
+      <c r="F60" s="3">
         <v>506500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>479300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>440900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>442200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>377800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>341800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>352300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>338300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>284400</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3222,8 +3501,14 @@
       <c r="S60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3275,44 +3560,50 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>224300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>227900</v>
+      </c>
+      <c r="F62" s="3">
         <v>229000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>226900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>235100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>236800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>232400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>234100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>230300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>240700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>235300</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>16</v>
       </c>
@@ -3328,8 +3619,14 @@
       <c r="S62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3381,8 +3678,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3434,8 +3737,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3487,44 +3796,50 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>825500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>819700</v>
+      </c>
+      <c r="F66" s="3">
         <v>735400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>706300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>676000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>679000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>610200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>575900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>582500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>579000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>519700</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>16</v>
       </c>
@@ -3540,8 +3855,14 @@
       <c r="S66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3561,8 +3882,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3614,8 +3937,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3667,8 +3996,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3697,14 +4032,14 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>949100</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -3720,8 +4055,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3773,44 +4114,50 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1511400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1455100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1341700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-1296200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-1236200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-1168400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-1114800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-1056200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-991900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-921000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-668200</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>16</v>
       </c>
@@ -3826,8 +4173,14 @@
       <c r="S72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3879,8 +4232,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3932,8 +4291,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3985,44 +4350,50 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>923900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>915100</v>
+      </c>
+      <c r="F76" s="3">
         <v>950900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>936400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>922600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>938000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>939800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>953100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>962400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>988900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-629200</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4038,8 +4409,14 @@
       <c r="S76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4091,119 +4468,137 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45416</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45325</v>
+      </c>
+      <c r="F80" s="2">
         <v>45227</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45136</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45045</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44954</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44863</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44772</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44590</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44499</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44317</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44226</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44044</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43953</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-56300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-113400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-45500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-60000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-67900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-53600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-58600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-64300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-71000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-252800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-32400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-31400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-38400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-36200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-54300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-56000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-63700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4223,41 +4618,43 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F83" s="3">
         <v>3600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>3700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>3500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>3400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>3300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>2600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>2400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>2200</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>16</v>
       </c>
@@ -4270,14 +4667,20 @@
       <c r="Q83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4329,8 +4732,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4382,8 +4791,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4435,8 +4850,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4488,8 +4909,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4541,41 +4968,47 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-41900</v>
+      </c>
+      <c r="F89" s="3">
         <v>11900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>7700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>10500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-4400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-12900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-37000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-48800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-48300</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>16</v>
       </c>
@@ -4588,14 +5021,20 @@
       <c r="Q89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4615,46 +5054,48 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-3400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-3000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-2500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-6000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-10300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-6300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-10700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-9400</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>16</v>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>16</v>
@@ -4662,14 +5103,20 @@
       <c r="Q91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4721,8 +5168,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4774,41 +5227,47 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-42600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-16900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-17700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-249300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-365600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-6300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-10700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-9500</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>16</v>
       </c>
@@ -4821,14 +5280,20 @@
       <c r="Q94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4848,8 +5313,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4901,8 +5368,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4954,8 +5427,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5007,8 +5486,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5060,41 +5545,47 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>12500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>6700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>9700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>703000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>16</v>
       </c>
@@ -5107,46 +5598,52 @@
       <c r="Q100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-200</v>
       </c>
       <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>16</v>
+      <c r="L101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-200</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>16</v>
@@ -5160,47 +5657,53 @@
       <c r="Q101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="F102" s="3">
         <v>9700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>3800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-7400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-246400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-379100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-33700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-61400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>645100</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>16</v>
       </c>
@@ -5213,10 +5716,16 @@
       <c r="Q102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
   <si>
     <t>IOT</t>
   </si>
@@ -656,277 +656,289 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45507</v>
+      </c>
+      <c r="E7" s="2">
         <v>45416</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45325</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45227</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45136</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45045</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44954</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44863</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44772</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44590</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44499</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44317</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44226</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44044</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43953</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>300200</v>
+      </c>
+      <c r="E8" s="3">
         <v>280700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>276300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>237500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>219300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>204300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>186600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>169800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>153500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>142600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>125800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>113800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>101000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>87700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>75900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>66200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>56800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>51000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>73400</v>
+      </c>
+      <c r="E9" s="3">
         <v>68600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>69000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>61600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>58900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>57600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>51500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>47300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>44300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>39600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>38700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>31800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>28400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>25600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>21200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>18700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>18900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>16600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>226800</v>
+      </c>
+      <c r="E10" s="3">
         <v>212100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>207300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>175900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>160400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>146700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>135100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>122500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>109200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>103000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>87100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>82000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>72600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>62100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>54700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>47500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>37900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>34400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -948,67 +960,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>76500</v>
+      </c>
+      <c r="E12" s="3">
         <v>73000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>73400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>60800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>64000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>60400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>54600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>50000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>41800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>41000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>126500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>29700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>25500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>23500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>20200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>33500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>21900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>24200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1066,23 +1082,26 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3">
         <v>68700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4800</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
@@ -1096,17 +1115,17 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>1100</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>1500</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1117,16 +1136,19 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>6800</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1184,8 +1206,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1204,126 +1229,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>358400</v>
+      </c>
+      <c r="E17" s="3">
         <v>346700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>399300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>292300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>289000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>280100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>246600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>233300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>219300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>212900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>377500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>146100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>132300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>126300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>111200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>120500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>112900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>114700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>109900</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-58200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-66000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-123000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-54800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-69700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-75800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-60000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-63500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-65800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-70300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-251700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-32300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-31300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-38600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-35300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-54300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-56100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-63700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-68300</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1345,126 +1377,133 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E20" s="3">
         <v>10100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>11400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>9400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>10200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>8900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1600</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-800</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
       </c>
       <c r="U20" s="3">
+        <v>100</v>
+      </c>
+      <c r="V20" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-51500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-106800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-41700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-55800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-63400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-48000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-54500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-61600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-67900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-249800</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R21" s="3">
         <v>-25400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-46000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1522,109 +1561,115 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-55900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-111500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-45400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-59500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-66900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-51500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-57900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-64200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-70300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-252000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-32400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-31000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-38400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-36200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-54300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-56000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-63600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>800</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -1638,10 +1683,13 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1699,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-49600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-56300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-113400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-45500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-60000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-67900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-53600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-58600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-64300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-71000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-252800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-32400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-31400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-38400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-36200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-54300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-56000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-63700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-49600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-56300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-113400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-45500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-60000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-67900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-53600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-58600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-64300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-71000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-252800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-32400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-31400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-38400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-36200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-54300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-56000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-63700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1876,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1935,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1994,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2053,126 +2119,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-11400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-9400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-10200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-8900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1600</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>800</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
       </c>
       <c r="U32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-49600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-56300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-113400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-45500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-60000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-67900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-53600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-58600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-64300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-71000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-252800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-32400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-31400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-38400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-36200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-54300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-56000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-63700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2230,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-49600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-56300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-113400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-45500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-60000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-67900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-53600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-58600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-64300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-71000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-252800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-32400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-31400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-38400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-36200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-54300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-56000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-63700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45507</v>
+      </c>
+      <c r="E38" s="2">
         <v>45416</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45325</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45227</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45136</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45045</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44954</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44863</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44772</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44590</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44499</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44317</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44226</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44044</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43953</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2376,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2399,47 +2484,48 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>159300</v>
+      </c>
+      <c r="E41" s="3">
         <v>162500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>135500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>208100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>196000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>192100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>200700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>447000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>826100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>859800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>921200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>267500</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2458,35 +2544,38 @@
       <c r="U41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>513400</v>
+      </c>
+      <c r="E42" s="3">
         <v>431900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>412100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>451700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>528800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>533900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>489200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>291800</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>16</v>
       </c>
@@ -2502,8 +2591,8 @@
       <c r="P42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2517,47 +2606,50 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>178800</v>
+      </c>
+      <c r="E43" s="3">
         <v>143800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>161800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>115200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>115400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>102600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>122900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>90800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>77400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>84900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>82000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>59400</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2576,47 +2668,50 @@
       <c r="U43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E44" s="3">
         <v>30500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>22200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>27100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>21800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>32400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>40600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>44500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>39100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>42000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>33100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>22300</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>16</v>
       </c>
@@ -2635,47 +2730,50 @@
       <c r="U44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>149600</v>
+      </c>
+      <c r="E45" s="3">
         <v>155100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>155200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>138800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>116000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>109600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>104200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>88900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>93400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>81900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>63900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>56800</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2694,47 +2792,50 @@
       <c r="U45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1039600</v>
+      </c>
+      <c r="E46" s="3">
         <v>923700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>887000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>940900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>978000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>970600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>957500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>963000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1036000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1068600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1100200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>406000</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>16</v>
       </c>
@@ -2753,35 +2854,38 @@
       <c r="U46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>207700</v>
+      </c>
+      <c r="E47" s="3">
         <v>250600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>276200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>189400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>109700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>87800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>113100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>63700</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>16</v>
       </c>
@@ -2797,8 +2901,8 @@
       <c r="P47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -2812,47 +2916,50 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>130200</v>
+      </c>
+      <c r="E48" s="3">
         <v>133300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>136900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>142100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>151100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>156100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>171900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>175900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>180100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>179200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>171200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>168800</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>16</v>
       </c>
@@ -2871,8 +2978,11 @@
       <c r="U48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2930,8 +3040,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2989,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3048,47 +3164,50 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>448600</v>
+      </c>
+      <c r="E52" s="3">
         <v>441800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>434800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>414000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>403900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>384100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>374500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>347400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>312900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>297100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>296600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>264700</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3107,8 +3226,11 @@
       <c r="U52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3166,47 +3288,50 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1826100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1749400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1734800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1686400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1642600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1598500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1617000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1550000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1529000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1545000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1567900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>839500</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3225,8 +3350,11 @@
       <c r="U54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3248,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3271,47 +3400,48 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E57" s="3">
         <v>41200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>46300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>38300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>34700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>29200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>30100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>43400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>20400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>40800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>54700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>42300</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3330,8 +3460,11 @@
       <c r="U57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3389,47 +3522,50 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>599800</v>
+      </c>
+      <c r="E59" s="3">
         <v>560100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>545500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>468200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>444700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>411600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>412000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>334500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>321400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>311500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>283600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>242100</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3448,47 +3584,50 @@
       <c r="U59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>647200</v>
+      </c>
+      <c r="E60" s="3">
         <v>601300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>591800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>506500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>479300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>440900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>442200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>377800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>341800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>352300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>338300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>284400</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3507,8 +3646,11 @@
       <c r="U60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3566,47 +3708,50 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>214300</v>
+      </c>
+      <c r="E62" s="3">
         <v>224300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>227900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>229000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>226900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>235100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>236800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>232400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>234100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>230300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>240700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>235300</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>16</v>
       </c>
@@ -3625,8 +3770,11 @@
       <c r="U62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3684,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3743,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3802,47 +3956,50 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>861500</v>
+      </c>
+      <c r="E66" s="3">
         <v>825500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>819700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>735400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>706300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>676000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>679000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>610200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>575900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>582500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>579000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>519700</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>16</v>
       </c>
@@ -3861,8 +4018,11 @@
       <c r="U66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3884,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3943,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4002,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4038,11 +4205,11 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>949100</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -4061,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4120,47 +4290,50 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1561000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1511400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1455100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1341700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1296200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1236200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1168400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1114800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1056200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-991900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-921000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-668200</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4179,8 +4352,11 @@
       <c r="U72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4238,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4297,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4356,47 +4538,50 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>964700</v>
+      </c>
+      <c r="E76" s="3">
         <v>923900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>915100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>950900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>936400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>922600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>938000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>939800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>953100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>962400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>988900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-629200</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4415,8 +4600,11 @@
       <c r="U76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4474,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45507</v>
+      </c>
+      <c r="E80" s="2">
         <v>45416</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45325</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45227</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45136</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45045</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44954</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44863</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44772</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44590</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44499</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44317</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44226</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44044</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43953</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-49600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-56300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-113400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-45500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-60000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-67900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-53600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-58600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-64300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-71000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-252800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-32400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-31400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-38400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-36200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-54300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-56000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-63700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4620,44 +4817,45 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E83" s="3">
         <v>4500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2200</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>16</v>
       </c>
@@ -4673,14 +4871,17 @@
       <c r="S83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4738,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4797,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4856,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4915,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4974,44 +5187,47 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E89" s="3">
         <v>23700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-41900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-37000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-48800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-48300</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5027,14 +5243,17 @@
       <c r="S89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
+      <c r="T89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5056,49 +5275,50 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9400</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>16</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>16</v>
@@ -5109,14 +5329,17 @@
       <c r="S91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5174,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5233,44 +5459,47 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-36300</v>
+      </c>
+      <c r="E94" s="3">
         <v>3100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-42600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-249300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-365600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-10700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9500</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5286,14 +5515,17 @@
       <c r="S94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5315,8 +5547,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5374,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5433,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5492,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5551,44 +5793,47 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>9000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>12500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>9700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>703000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>16</v>
       </c>
@@ -5604,40 +5849,43 @@
       <c r="S100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
+      <c r="T100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-200</v>
       </c>
       <c r="L101" s="3">
         <v>-200</v>
@@ -5645,8 +5893,8 @@
       <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>16</v>
+      <c r="N101" s="3">
+        <v>-200</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>16</v>
@@ -5663,50 +5911,53 @@
       <c r="S101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E102" s="3">
         <v>26900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-75000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-246400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-379100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-33700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-61400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>645100</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>16</v>
       </c>
@@ -5722,10 +5973,13 @@
       <c r="S102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
+      <c r="T102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
   <si>
     <t>IOT</t>
   </si>
@@ -656,289 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45598</v>
+      </c>
+      <c r="E7" s="2">
         <v>45507</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45416</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45325</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45227</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45136</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45045</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44954</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44863</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44772</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44590</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44499</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44317</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44226</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44044</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43953</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>322000</v>
+      </c>
+      <c r="E8" s="3">
         <v>300200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>280700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>276300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>237500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>219300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>204300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>186600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>169800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>153500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>142600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>125800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>113800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>101000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>87700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>75900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>66200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>56800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>51000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>73400</v>
+        <v>76000</v>
       </c>
       <c r="E9" s="3">
+        <v>73200</v>
+      </c>
+      <c r="F9" s="3">
         <v>68600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>69000</v>
       </c>
-      <c r="G9" s="3">
-        <v>61600</v>
-      </c>
       <c r="H9" s="3">
-        <v>58900</v>
+        <v>61400</v>
       </c>
       <c r="I9" s="3">
+        <v>58600</v>
+      </c>
+      <c r="J9" s="3">
         <v>57600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>51500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>47300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>44300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>39600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>38700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>31800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>28400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>25600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>21200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>18700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>18900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>16600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>226800</v>
+        <v>246000</v>
       </c>
       <c r="E10" s="3">
+        <v>227000</v>
+      </c>
+      <c r="F10" s="3">
         <v>212100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>207300</v>
       </c>
-      <c r="G10" s="3">
-        <v>175900</v>
-      </c>
       <c r="H10" s="3">
-        <v>160400</v>
+        <v>176100</v>
       </c>
       <c r="I10" s="3">
-        <v>146700</v>
+        <v>160600</v>
       </c>
       <c r="J10" s="3">
+        <v>146800</v>
+      </c>
+      <c r="K10" s="3">
         <v>135100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>122500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>109200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>103000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>87100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>82000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>72600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>62100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>54700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>47500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>37900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>34400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -961,70 +973,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E12" s="3">
         <v>76500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>73000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>73400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>60800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>64000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>60400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>54600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>50000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>41800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>41000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>126500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>29700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>25500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>23500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>20200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>33500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>21900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>24200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1085,31 +1101,34 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>16</v>
+      <c r="D14" s="3">
+        <v>3600</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3">
         <v>68700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4800</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1118,17 +1137,17 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>1100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>1500</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1139,39 +1158,42 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>6800</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1209,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>365700</v>
+      </c>
+      <c r="E17" s="3">
         <v>358400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>346700</v>
       </c>
-      <c r="F17" s="3">
-        <v>399300</v>
-      </c>
       <c r="G17" s="3">
-        <v>292300</v>
+        <v>330600</v>
       </c>
       <c r="H17" s="3">
+        <v>287500</v>
+      </c>
+      <c r="I17" s="3">
         <v>289000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>280100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>246600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>233300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>219300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>212900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>377500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>146100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>132300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>126300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>111200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>120500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>112900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>114700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>109900</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-43800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-58200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-66000</v>
       </c>
-      <c r="F18" s="3">
-        <v>-123000</v>
-      </c>
       <c r="G18" s="3">
-        <v>-54800</v>
+        <v>-54300</v>
       </c>
       <c r="H18" s="3">
-        <v>-69700</v>
+        <v>-50000</v>
       </c>
       <c r="I18" s="3">
+        <v>-69800</v>
+      </c>
+      <c r="J18" s="3">
         <v>-75800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-60000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-63500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-65800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-70300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-251700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-32300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-38600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-35300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-54300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-56100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-63700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-68300</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1378,155 +1410,162 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
-        <v>9600</v>
-      </c>
-      <c r="E20" s="3">
-        <v>10100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>11400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>9400</v>
-      </c>
-      <c r="H20" s="3">
-        <v>10200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>8900</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" s="3">
         <v>8500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1600</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-800</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3">
         <v>100</v>
       </c>
       <c r="V20" s="3">
+        <v>100</v>
+      </c>
+      <c r="W20" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-43900</v>
+        <v>-37000</v>
       </c>
       <c r="E21" s="3">
-        <v>-51500</v>
+        <v>-53600</v>
       </c>
       <c r="F21" s="3">
-        <v>-106800</v>
+        <v>-61500</v>
       </c>
       <c r="G21" s="3">
-        <v>-41700</v>
+        <v>-51100</v>
       </c>
       <c r="H21" s="3">
-        <v>-55800</v>
+        <v>-47600</v>
       </c>
       <c r="I21" s="3">
-        <v>-63400</v>
+        <v>-66000</v>
       </c>
       <c r="J21" s="3">
+        <v>-72300</v>
+      </c>
+      <c r="K21" s="3">
         <v>-48000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-54500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-61600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-67900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-249800</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S21" s="3">
         <v>-25400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-46000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1564,115 +1603,121 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-37300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-48600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-55900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-111500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-45400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-59500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-66900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-51500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-57900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-64200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-70300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-252000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-32400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-31000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-38400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-36200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-54300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-56000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-63600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>800</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -1686,10 +1731,13 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-49600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-56300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-113400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-45500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-60000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-67900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-53600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-58600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-64300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-71000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-252800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-32400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-38400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-36200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-54300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-56000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-63700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-49600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-56300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-113400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-45500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-60000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-67900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-53600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-58600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-64300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-71000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-252800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-32400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-38400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-36200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-54300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-56000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-63700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-10100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-11400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K32" s="3">
         <v>-8500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1600</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>800</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3">
         <v>-100</v>
       </c>
       <c r="V32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W32" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-49600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-56300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-113400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-45500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-60000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-67900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-53600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-58600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-64300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-71000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-252800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-32400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-38400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-36200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-54300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-56000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-63700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-49600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-56300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-113400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-45500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-60000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-67900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-53600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-58600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-64300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-71000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-252800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-32400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-38400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-36200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-54300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-56000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-63700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45598</v>
+      </c>
+      <c r="E38" s="2">
         <v>45507</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45416</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45325</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45227</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45136</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45045</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44954</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44863</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44772</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44590</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44499</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44317</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44226</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44044</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43953</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,50 +2570,51 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>160300</v>
+      </c>
+      <c r="E41" s="3">
         <v>159300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>162500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>135500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>208100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>196000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>192100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>200700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>447000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>826100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>859800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>921200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>267500</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2547,38 +2633,41 @@
       <c r="V41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>511600</v>
+      </c>
+      <c r="E42" s="3">
         <v>513400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>431900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>412100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>451700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>528800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>533900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>489200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>291800</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>16</v>
       </c>
@@ -2594,8 +2683,8 @@
       <c r="Q42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2609,50 +2698,53 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>178800</v>
+        <v>178700</v>
       </c>
       <c r="E43" s="3">
-        <v>143800</v>
+        <v>183600</v>
       </c>
       <c r="F43" s="3">
+        <v>148800</v>
+      </c>
+      <c r="G43" s="3">
         <v>161800</v>
       </c>
-      <c r="G43" s="3">
-        <v>115200</v>
-      </c>
       <c r="H43" s="3">
-        <v>115400</v>
+        <v>119500</v>
       </c>
       <c r="I43" s="3">
-        <v>102600</v>
+        <v>118600</v>
       </c>
       <c r="J43" s="3">
+        <v>105200</v>
+      </c>
+      <c r="K43" s="3">
         <v>122900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>90800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>77400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>84900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>82000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>59400</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2671,50 +2763,53 @@
       <c r="V43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E44" s="3">
         <v>38600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>30500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>22200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>27100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>21800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>32400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>40600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>44500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>39100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>42000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>33100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>22300</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>16</v>
       </c>
@@ -2733,50 +2828,53 @@
       <c r="V44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>149600</v>
+        <v>115100</v>
       </c>
       <c r="E45" s="3">
-        <v>155100</v>
+        <v>111300</v>
       </c>
       <c r="F45" s="3">
-        <v>155200</v>
+        <v>107800</v>
       </c>
       <c r="G45" s="3">
-        <v>138800</v>
+        <v>104000</v>
       </c>
       <c r="H45" s="3">
-        <v>116000</v>
+        <v>99200</v>
       </c>
       <c r="I45" s="3">
-        <v>109600</v>
+        <v>94100</v>
       </c>
       <c r="J45" s="3">
+        <v>86300</v>
+      </c>
+      <c r="K45" s="3">
         <v>104200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>88900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>93400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>81900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>63900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>56800</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2795,50 +2893,53 @@
       <c r="V45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1039400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1039600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>923700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>887000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>940900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>978000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>970600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>957500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>963000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1036000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1068600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1100200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>406000</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>16</v>
       </c>
@@ -2857,38 +2958,41 @@
       <c r="V46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>241100</v>
+      </c>
+      <c r="E47" s="3">
         <v>207700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>250600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>276200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>189400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>109700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>87800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>113100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>63700</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>16</v>
       </c>
@@ -2904,8 +3008,8 @@
       <c r="Q47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -2919,50 +3023,53 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>125600</v>
+      </c>
+      <c r="E48" s="3">
         <v>130200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>133300</v>
       </c>
-      <c r="F48" s="3">
-        <v>136900</v>
-      </c>
       <c r="G48" s="3">
-        <v>142100</v>
+        <v>124500</v>
       </c>
       <c r="H48" s="3">
-        <v>151100</v>
+        <v>129100</v>
       </c>
       <c r="I48" s="3">
-        <v>156100</v>
+        <v>139900</v>
       </c>
       <c r="J48" s="3">
+        <v>146500</v>
+      </c>
+      <c r="K48" s="3">
         <v>171900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>175900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>180100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>179200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>171200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>168800</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>16</v>
       </c>
@@ -2981,8 +3088,11 @@
       <c r="V48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2996,16 +3106,16 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>12500</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="I49" s="3">
-        <v>0</v>
+        <v>11200</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -3043,8 +3153,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,50 +3283,53 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>448600</v>
+        <v>26900</v>
       </c>
       <c r="E52" s="3">
-        <v>441800</v>
+        <v>25800</v>
       </c>
       <c r="F52" s="3">
-        <v>434800</v>
+        <v>26100</v>
       </c>
       <c r="G52" s="3">
-        <v>414000</v>
+        <v>26400</v>
       </c>
       <c r="H52" s="3">
-        <v>403900</v>
+        <v>37800</v>
       </c>
       <c r="I52" s="3">
-        <v>384100</v>
+        <v>40100</v>
       </c>
       <c r="J52" s="3">
+        <v>40100</v>
+      </c>
+      <c r="K52" s="3">
         <v>374500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>347400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>312900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>297100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>296600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>264700</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3229,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,50 +3413,53 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1863900</v>
+      </c>
+      <c r="E54" s="3">
         <v>1826100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1749400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1734800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1686400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1642600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1598500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1617000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1550000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1529000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1545000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1567900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>839500</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3353,8 +3478,11 @@
       <c r="V54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,50 +3530,51 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E57" s="3">
         <v>47300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>41200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>46300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>38300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>34700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>30100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>43400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>20400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>40800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>54700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>42300</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3463,31 +3593,34 @@
       <c r="V57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>19400</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>20700</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>20500</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>16500</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3525,50 +3658,53 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>599800</v>
+        <v>505600</v>
       </c>
       <c r="E59" s="3">
-        <v>560100</v>
+        <v>485900</v>
       </c>
       <c r="F59" s="3">
-        <v>545500</v>
+        <v>447000</v>
       </c>
       <c r="G59" s="3">
-        <v>468200</v>
+        <v>426400</v>
       </c>
       <c r="H59" s="3">
-        <v>444700</v>
+        <v>367400</v>
       </c>
       <c r="I59" s="3">
-        <v>411600</v>
+        <v>348800</v>
       </c>
       <c r="J59" s="3">
+        <v>319100</v>
+      </c>
+      <c r="K59" s="3">
         <v>412000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>334500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>321400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>311500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>283600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>242100</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3587,50 +3723,53 @@
       <c r="V59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>654100</v>
+      </c>
+      <c r="E60" s="3">
         <v>647200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>601300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>591800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>506500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>479300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>440900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>442200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>377800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>341800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>352300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>338300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>284400</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3649,31 +3788,34 @@
       <c r="V60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>68000</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>68300</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>73600</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>78800</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>83300</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>89400</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>95200</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3711,50 +3853,53 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>214300</v>
+        <v>8500</v>
       </c>
       <c r="E62" s="3">
-        <v>224300</v>
+        <v>9200</v>
       </c>
       <c r="F62" s="3">
-        <v>227900</v>
+        <v>9600</v>
       </c>
       <c r="G62" s="3">
-        <v>229000</v>
+        <v>9900</v>
       </c>
       <c r="H62" s="3">
-        <v>226900</v>
+        <v>9300</v>
       </c>
       <c r="I62" s="3">
-        <v>235100</v>
+        <v>9300</v>
       </c>
       <c r="J62" s="3">
+        <v>9100</v>
+      </c>
+      <c r="K62" s="3">
         <v>236800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>232400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>234100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>230300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>240700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>235300</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>16</v>
       </c>
@@ -3773,8 +3918,11 @@
       <c r="V62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,50 +4113,53 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>864700</v>
+      </c>
+      <c r="E66" s="3">
         <v>861500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>825500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>819700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>735400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>706300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>676000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>679000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>610200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>575900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>582500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>579000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>519700</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4021,8 +4178,11 @@
       <c r="V66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4208,11 +4375,11 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>949100</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -4231,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,50 +4463,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1598800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1561000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1511400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1455100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1341700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1296200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1236200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1168400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1114800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1056200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-991900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-921000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-668200</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4355,8 +4528,11 @@
       <c r="V72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,50 +4723,53 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>999100</v>
+      </c>
+      <c r="E76" s="3">
         <v>964700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>923900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>915100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>950900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>936400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>922600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>938000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>939800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>953100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>962400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>988900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-629200</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4603,8 +4788,11 @@
       <c r="V76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45598</v>
+      </c>
+      <c r="E80" s="2">
         <v>45507</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45416</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45325</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45227</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45136</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45045</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44954</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44863</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44772</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44590</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44499</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44317</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44226</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44044</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43953</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-49600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-56300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-113400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-45500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-60000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-67900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-53600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-58600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-64300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-71000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-252800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-32400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-38400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-36200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-54300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-56000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-63700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,47 +5015,48 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4600</v>
+        <v>2500</v>
       </c>
       <c r="E83" s="3">
-        <v>4500</v>
+        <v>3700</v>
       </c>
       <c r="F83" s="3">
-        <v>4700</v>
+        <v>3500</v>
       </c>
       <c r="G83" s="3">
-        <v>3600</v>
+        <v>2400</v>
       </c>
       <c r="H83" s="3">
-        <v>3700</v>
+        <v>2400</v>
       </c>
       <c r="I83" s="3">
-        <v>3500</v>
+        <v>1600</v>
       </c>
       <c r="J83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K83" s="3">
         <v>3400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2200</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>16</v>
       </c>
@@ -4874,14 +5072,17 @@
       <c r="T83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,47 +5403,50 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E89" s="3">
         <v>18100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>23700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-41900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-12900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-37000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-48800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-48300</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5246,14 +5462,17 @@
       <c r="T89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
+      <c r="U89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,52 +5495,53 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-9400</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>16</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>16</v>
@@ -5332,14 +5552,17 @@
       <c r="T91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,47 +5688,50 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-33900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-36300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-42600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-17700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-249300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-365600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9500</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5518,14 +5747,17 @@
       <c r="T94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,31 +5780,32 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5610,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,47 +6038,50 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E100" s="3">
         <v>15700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>9000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>12500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>9700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>703000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>16</v>
       </c>
@@ -5852,14 +6097,17 @@
       <c r="T100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
+      <c r="U100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5867,28 +6115,28 @@
         <v>-500</v>
       </c>
       <c r="E101" s="3">
+        <v>400</v>
+      </c>
+      <c r="F101" s="3">
+        <v>100</v>
+      </c>
+      <c r="G101" s="3">
+        <v>600</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>500</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H101" s="3">
-        <v>400</v>
-      </c>
       <c r="I101" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="J101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-200</v>
       </c>
       <c r="M101" s="3">
         <v>-200</v>
@@ -5896,8 +6144,8 @@
       <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>16</v>
+      <c r="O101" s="3">
+        <v>-200</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>16</v>
@@ -5914,53 +6162,56 @@
       <c r="T101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>26900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-75000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-246400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-379100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-33700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-61400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>645100</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>16</v>
       </c>
@@ -5976,10 +6227,13 @@
       <c r="T102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
+      <c r="U102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>IOT</t>
   </si>
@@ -656,301 +656,313 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E7" s="2">
         <v>45598</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45507</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45416</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45325</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45227</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45136</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45045</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44954</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44863</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44772</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44590</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44499</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44317</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44226</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44044</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43953</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>346300</v>
+      </c>
+      <c r="E8" s="3">
         <v>322000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>300200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>280700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>276300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>237500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>219300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>204300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>186600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>169800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>153500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>142600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>125800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>113800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>101000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>87700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>75900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>66200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>56800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>51000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>76000</v>
+        <v>80300</v>
       </c>
       <c r="E9" s="3">
+        <v>75700</v>
+      </c>
+      <c r="F9" s="3">
         <v>73200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>68600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>69000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>61400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>58600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>57600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>51500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>47300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>44300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>39600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>38700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>31800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>28400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>25600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>21200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>18700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>18900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>16600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>246000</v>
+        <v>266000</v>
       </c>
       <c r="E10" s="3">
+        <v>246300</v>
+      </c>
+      <c r="F10" s="3">
         <v>227000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>212100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>207300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>176100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>160600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>146800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>135100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>122500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>109200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>103000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>87100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>82000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>72600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>62100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>54700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>47500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>37900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>34400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,73 +986,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E12" s="3">
         <v>77000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>76500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>73000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>73400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>60800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>64000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>60400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>54600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>50000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>41800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>41000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>126500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>29700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>25500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>23500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>20200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>33500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>21900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>24200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1104,34 +1120,37 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E14" s="3">
         <v>3600</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="3">
         <v>68700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4800</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1140,17 +1159,17 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>1100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1500</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1161,43 +1180,46 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>6800</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E15" s="3">
         <v>6800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3300</v>
       </c>
-      <c r="H15" s="3">
-        <v>2500</v>
-      </c>
       <c r="I15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J15" s="3">
         <v>3700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3500</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1234,8 +1256,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1281,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>363400</v>
+      </c>
+      <c r="E17" s="3">
         <v>365700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>358400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>346700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>330600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>287500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>289000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>280100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>246600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>233300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>219300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>212900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>377500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>146100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>132300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>126300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>111200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>120500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>112900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>114700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>109900</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-43800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-58200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-66000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-54300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-50000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-69800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-75800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-60000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-63500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-65800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-70300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-251700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-32300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-31300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-38600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-35300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-54300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-56100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-63700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-68300</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1411,8 +1443,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1437,112 +1470,118 @@
       <c r="J20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L20" s="3">
         <v>8500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1600</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-800</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>100</v>
       </c>
       <c r="W20" s="3">
+        <v>100</v>
+      </c>
+      <c r="X20" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-37000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-53600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-61500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-51100</v>
       </c>
-      <c r="H21" s="3">
-        <v>-47600</v>
-      </c>
       <c r="I21" s="3">
+        <v>-46400</v>
+      </c>
+      <c r="J21" s="3">
         <v>-66000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-72300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-48000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-54500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-61600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-67900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-249800</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T21" s="3">
         <v>-25400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-46000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1567,8 +1606,8 @@
       <c r="J22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1606,121 +1645,127 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-37300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-48600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-55900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-111500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-45400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-59500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-66900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-51500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-57900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-64200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-70300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-252000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-32400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-31000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-38400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-36200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-54300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-56000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-63600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>800</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -1734,10 +1779,13 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1849,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-37800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-49600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-56300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-113400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-45500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-60000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-67900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-53600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-58600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-64300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-71000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-252800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-32400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-31400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-38400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-36200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-54300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-56000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-63700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-37800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-49600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-56300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-113400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-45500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-60000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-67900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-53600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-58600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-64300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-71000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-252800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-32400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-31400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-38400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-36200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-54300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-56000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-63700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2053,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2121,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2189,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,8 +2257,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2217,112 +2286,118 @@
       <c r="J32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L32" s="3">
         <v>-8500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1600</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>800</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
         <v>-100</v>
       </c>
       <c r="W32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X32" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-37800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-49600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-56300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-113400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-45500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-60000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-67900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-53600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-58600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-64300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-71000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-252800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-32400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-31400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-38400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-36200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-54300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-56000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-63700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2461,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-37800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-49600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-56300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-113400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-45500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-60000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-67900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-53600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-58600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-64300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-71000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-252800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-32400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-31400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-38400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-36200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-54300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-56000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-63700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E38" s="2">
         <v>45598</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45507</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45416</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45325</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45227</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45136</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45045</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44954</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44863</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44772</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44590</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44499</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44317</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44226</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44044</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43953</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2630,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,53 +2656,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>227600</v>
+      </c>
+      <c r="E41" s="3">
         <v>160300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>159300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>162500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>135500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>208100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>196000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>192100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>200700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>447000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>826100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>859800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>921200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>267500</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2636,41 +2722,44 @@
       <c r="W41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>467200</v>
+      </c>
+      <c r="E42" s="3">
         <v>511600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>513400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>431900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>412100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>451700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>528800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>533900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>489200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>291800</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>16</v>
       </c>
@@ -2686,8 +2775,8 @@
       <c r="R42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -2701,53 +2790,56 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>178700</v>
+        <v>234000</v>
       </c>
       <c r="E43" s="3">
+        <v>184300</v>
+      </c>
+      <c r="F43" s="3">
         <v>183600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>148800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>161800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>119500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>118600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>105200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>122900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>90800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>77400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>84900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>82000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>59400</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2766,53 +2858,56 @@
       <c r="W43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E44" s="3">
         <v>39400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>38600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>30500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>22200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>27100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>21800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>32400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>40600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>44500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>39100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>42000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>33100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>22300</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>16</v>
       </c>
@@ -2831,53 +2926,56 @@
       <c r="W44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>119300</v>
+      </c>
+      <c r="E45" s="3">
         <v>115100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>111300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>107800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>104000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>99200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>94100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>86300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>104200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>88900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>93400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>81900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>63900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>56800</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2896,53 +2994,56 @@
       <c r="W45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1145200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1039400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1039600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>923700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>887000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>940900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>978000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>970600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>957500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>963000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1036000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1068600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1100200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>406000</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>16</v>
       </c>
@@ -2961,41 +3062,44 @@
       <c r="W46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>282700</v>
+      </c>
+      <c r="E47" s="3">
         <v>241100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>207700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>250600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>276200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>189400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>109700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>87800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>113100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>63700</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3011,8 +3115,8 @@
       <c r="R47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -3026,53 +3130,56 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>123000</v>
+      </c>
+      <c r="E48" s="3">
         <v>125600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>130200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>133300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>124500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>129100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>139900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>146500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>171900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>175900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>180100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>179200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>171200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>168800</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3091,8 +3198,11 @@
       <c r="W48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3106,20 +3216,20 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>12500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9600</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
@@ -3156,8 +3266,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3334,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,53 +3402,56 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E52" s="3">
         <v>26900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>25800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>26100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>26400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>37800</v>
-      </c>
-      <c r="I52" s="3">
-        <v>40100</v>
       </c>
       <c r="J52" s="3">
         <v>40100</v>
       </c>
       <c r="K52" s="3">
+        <v>40100</v>
+      </c>
+      <c r="L52" s="3">
         <v>374500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>347400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>312900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>297100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>296600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>264700</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3351,8 +3470,11 @@
       <c r="W52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,53 +3538,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2024300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1863900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1826100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1749400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1734800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1686400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1642600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1598500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1617000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1550000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1529000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1545000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1567900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>839500</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3481,8 +3606,11 @@
       <c r="W54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3634,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,53 +3660,54 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E57" s="3">
         <v>31500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>47300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>41200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>46300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>38300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>34700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>29200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>30100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>43400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>20400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>40800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>54700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>42300</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3596,35 +3726,38 @@
       <c r="W57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E58" s="3">
         <v>18000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>19400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>20000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>20700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>16500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -3661,53 +3794,56 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>563300</v>
+      </c>
+      <c r="E59" s="3">
         <v>505600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>485900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>447000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>426400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>367400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>348800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>319100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>412000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>334500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>321400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>311500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>283600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>242100</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3726,53 +3862,56 @@
       <c r="W59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>761300</v>
+      </c>
+      <c r="E60" s="3">
         <v>654100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>647200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>601300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>591800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>506500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>479300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>440900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>442200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>377800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>341800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>352300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>338300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>284400</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3791,35 +3930,38 @@
       <c r="W60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>64600</v>
+      </c>
+      <c r="E61" s="3">
         <v>68000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>68300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>73600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>78800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>83300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>89400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>95200</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3856,53 +3998,56 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E62" s="3">
         <v>8500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9900</v>
-      </c>
-      <c r="H62" s="3">
-        <v>9300</v>
       </c>
       <c r="I62" s="3">
         <v>9300</v>
       </c>
       <c r="J62" s="3">
+        <v>9300</v>
+      </c>
+      <c r="K62" s="3">
         <v>9100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>236800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>232400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>234100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>230300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>240700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>235300</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>16</v>
       </c>
@@ -3921,8 +4066,11 @@
       <c r="W62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4134,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4202,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,53 +4270,56 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>955100</v>
+      </c>
+      <c r="E66" s="3">
         <v>864700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>861500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>825500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>819700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>735400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>706300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>676000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>679000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>610200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>575900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>582500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>579000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>519700</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4181,8 +4338,11 @@
       <c r="W66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4366,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4432,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4500,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4378,11 +4545,11 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>949100</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4401,8 +4568,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,53 +4636,56 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1610000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1598800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1561000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1511400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1455100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1341700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1296200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1236200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1168400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1114800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1056200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-991900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-921000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-668200</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4531,8 +4704,11 @@
       <c r="W72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4772,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4840,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,53 +4908,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1069200</v>
+      </c>
+      <c r="E76" s="3">
         <v>999100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>964700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>923900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>915100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>950900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>936400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>922600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>938000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>939800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>953100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>962400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>988900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-629200</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4791,8 +4976,11 @@
       <c r="W76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5044,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E80" s="2">
         <v>45598</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45507</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45416</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45325</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45227</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45136</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45045</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44954</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44863</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44772</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44590</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44499</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44317</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44226</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44044</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43953</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-37800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-49600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-56300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-113400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-45500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-60000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-67900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-53600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-58600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-64300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-71000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-252800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-32400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-31400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-38400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-36200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-54300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-56000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-63700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,50 +5213,51 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="E83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F83" s="3">
         <v>3700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3500</v>
-      </c>
-      <c r="G83" s="3">
-        <v>2400</v>
       </c>
       <c r="H83" s="3">
         <v>2400</v>
       </c>
       <c r="I83" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J83" s="3">
         <v>1600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2200</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5075,14 +5273,17 @@
       <c r="U83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5347,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5415,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5483,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5551,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,50 +5619,53 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>53900</v>
+      </c>
+      <c r="E89" s="3">
         <v>36000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>18100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>23700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-41900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-12900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-37000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-48800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-48300</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5465,14 +5681,17 @@
       <c r="U89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
+      <c r="V89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,55 +5715,56 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9400</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>16</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>16</v>
@@ -5555,14 +5775,17 @@
       <c r="U91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5849,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,50 +5917,53 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-33900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-36300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-42600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-17700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-249300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-365600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9500</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5750,14 +5979,17 @@
       <c r="U94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6013,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5807,8 +6040,8 @@
       <c r="J96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5846,8 +6079,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6147,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6215,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,50 +6283,53 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>15700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>9000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>12500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>9700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>703000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6100,46 +6345,49 @@
       <c r="U100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
+      <c r="V100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-200</v>
       </c>
       <c r="J101" s="3">
         <v>-200</v>
       </c>
       <c r="K101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-200</v>
       </c>
       <c r="N101" s="3">
         <v>-200</v>
@@ -6147,8 +6395,8 @@
       <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>16</v>
+      <c r="P101" s="3">
+        <v>-200</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>16</v>
@@ -6165,56 +6413,59 @@
       <c r="U101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E102" s="3">
         <v>1900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>26900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-75000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-246400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-379100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-33700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-61400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>645100</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6230,10 +6481,13 @@
       <c r="U102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
+      <c r="V102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
   <si>
     <t>IOT</t>
   </si>
@@ -831,7 +831,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>80300</v>
+        <v>79300</v>
       </c>
       <c r="E9" s="3">
         <v>75700</v>
@@ -843,7 +843,7 @@
         <v>68600</v>
       </c>
       <c r="H9" s="3">
-        <v>69000</v>
+        <v>68200</v>
       </c>
       <c r="I9" s="3">
         <v>61400</v>
@@ -899,7 +899,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>266000</v>
+        <v>267000</v>
       </c>
       <c r="E10" s="3">
         <v>246300</v>
@@ -911,7 +911,7 @@
         <v>212100</v>
       </c>
       <c r="H10" s="3">
-        <v>207300</v>
+        <v>208100</v>
       </c>
       <c r="I10" s="3">
         <v>176100</v>
@@ -1449,8 +1449,8 @@
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>16</v>
+      <c r="D20" s="3">
+        <v>2700</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>16</v>
@@ -1461,8 +1461,8 @@
       <c r="G20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>16</v>
+      <c r="H20" s="3">
+        <v>100</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>16</v>
@@ -1518,7 +1518,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-12300</v>
+        <v>-15100</v>
       </c>
       <c r="E21" s="3">
         <v>-37000</v>
@@ -1530,7 +1530,7 @@
         <v>-61500</v>
       </c>
       <c r="H21" s="3">
-        <v>-51100</v>
+        <v>-51200</v>
       </c>
       <c r="I21" s="3">
         <v>-46400</v>
@@ -2265,8 +2265,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>16</v>
+      <c r="D32" s="3">
+        <v>-2700</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>16</v>
@@ -2277,8 +2277,8 @@
       <c r="G32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>16</v>
+      <c r="H32" s="3">
+        <v>-100</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>16</v>
@@ -2799,7 +2799,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>234000</v>
+        <v>240200</v>
       </c>
       <c r="E43" s="3">
         <v>184300</v>
@@ -2811,7 +2811,7 @@
         <v>148800</v>
       </c>
       <c r="H43" s="3">
-        <v>161800</v>
+        <v>166700</v>
       </c>
       <c r="I43" s="3">
         <v>119500</v>
@@ -3151,7 +3151,7 @@
         <v>133300</v>
       </c>
       <c r="H48" s="3">
-        <v>124500</v>
+        <v>136900</v>
       </c>
       <c r="I48" s="3">
         <v>129100</v>
@@ -3219,7 +3219,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>12500</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
         <v>13000</v>
@@ -5220,7 +5220,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3300</v>
+        <v>-100</v>
       </c>
       <c r="E83" s="3">
         <v>3600</v>

--- a/AAII_Financials/Quarterly/IOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
   <si>
     <t>IOT</t>
   </si>
@@ -656,313 +656,325 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45780</v>
+      </c>
+      <c r="E7" s="2">
         <v>45689</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45598</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45507</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45416</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45325</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45227</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45136</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45045</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44954</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44863</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44772</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44590</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44499</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44317</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44226</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44044</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43953</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>366900</v>
+      </c>
+      <c r="E8" s="3">
         <v>346300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>322000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>300200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>280700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>276300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>237500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>219300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>204300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>186600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>169800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>153500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>142600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>125800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>113800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>101000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>87700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>75900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>66200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>56800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>51000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>82800</v>
+      </c>
+      <c r="E9" s="3">
         <v>79300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>75700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>73200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>68600</v>
       </c>
       <c r="H9" s="3">
         <v>68200</v>
       </c>
       <c r="I9" s="3">
+        <v>68200</v>
+      </c>
+      <c r="J9" s="3">
         <v>61400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>58600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>57600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>51500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>47300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>44300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>39600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>38700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>31800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>28400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>25600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>21200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>18700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>18900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>16600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>284100</v>
+      </c>
+      <c r="E10" s="3">
         <v>267000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>246300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>227000</v>
       </c>
-      <c r="G10" s="3">
-        <v>212100</v>
-      </c>
       <c r="H10" s="3">
+        <v>212500</v>
+      </c>
+      <c r="I10" s="3">
         <v>208100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>176100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>160600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>146800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>135100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>122500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>109200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>103000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>87100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>82000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>72600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>62100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>54700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>47500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>37900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>34400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -987,76 +999,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>83200</v>
+      </c>
+      <c r="E12" s="3">
         <v>73300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>77000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>76500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>73000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>73400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>60800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>64000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>60400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>54600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>50000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>41800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>41000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>126500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>29700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>25500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>23500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>20200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>33500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>21900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>24200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1123,37 +1139,40 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="3">
         <v>1300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3600</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3">
         <v>68700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4800</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1162,17 +1181,17 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>1100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>1500</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
@@ -1183,46 +1202,49 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>6800</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E15" s="3">
         <v>4800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4600</v>
       </c>
-      <c r="G15" s="3">
-        <v>4500</v>
-      </c>
       <c r="H15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I15" s="3">
         <v>3300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3500</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1259,8 +1281,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1282,144 +1307,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>400100</v>
+      </c>
+      <c r="E17" s="3">
         <v>363400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>365700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>358400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>346700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>330600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>287500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>289000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>280100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>246600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>233300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>219300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>212900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>377500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>146100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>132300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>126300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>111200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>120500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>112900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>114700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>109900</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-17100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-43800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-58200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-66000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-54300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-50000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-69800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-75800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-60000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-63500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-65800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-70300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-251700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-32300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-31300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-38600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-35300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-54300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-56100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-63700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-68300</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1444,17 +1476,18 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E20" s="3">
         <v>2700</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
@@ -1462,126 +1495,132 @@
         <v>16</v>
       </c>
       <c r="H20" s="3">
+        <v>300</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>16</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M20" s="3">
         <v>8500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1600</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-800</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3">
         <v>100</v>
       </c>
       <c r="X20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y20" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-29600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-15100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-37000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-53600</v>
       </c>
-      <c r="G21" s="3">
-        <v>-61500</v>
-      </c>
       <c r="H21" s="3">
+        <v>-63800</v>
+      </c>
+      <c r="I21" s="3">
         <v>-51200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-46400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-66000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-72300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-48000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-54500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-61600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-67900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-249800</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U21" s="3">
         <v>-25400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-46000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1609,8 +1648,8 @@
       <c r="K22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1648,127 +1687,133 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-37300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-48600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-55900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-111500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-45400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-59500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-66900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-51500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-57900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-64200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-70300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-252000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-32400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-31000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-38400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-36200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-54300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-56000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-63600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E24" s="3">
         <v>2600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>800</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
@@ -1782,10 +1827,13 @@
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1852,144 +1900,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-11200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-37800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-49600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-56300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-113400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-45500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-60000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-67900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-53600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-58600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-64300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-71000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-252800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-32400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-31400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-38400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-36200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-54300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-56000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-63700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-37800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-49600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-56300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-113400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-45500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-60000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-67900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-53600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-58600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-64300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-71000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-252800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-32400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-31400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-38400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-36200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-54300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-56000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-63700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2056,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2124,8 +2184,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2192,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2260,17 +2326,20 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2700</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F32" s="3" t="s">
         <v>16</v>
       </c>
@@ -2278,126 +2347,132 @@
         <v>16</v>
       </c>
       <c r="H32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M32" s="3">
         <v>-8500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1600</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>800</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W32" s="3">
         <v>-100</v>
       </c>
       <c r="X32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-37800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-49600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-56300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-113400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-45500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-60000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-67900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-53600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-58600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-64300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-71000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-252800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-32400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-31400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-38400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-36200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-54300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-56000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-63700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2464,149 +2539,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-37800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-49600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-56300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-113400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-45500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-60000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-67900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-53600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-58600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-64300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-71000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-252800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-32400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-31400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-38400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-36200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-54300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-56000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-63700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45780</v>
+      </c>
+      <c r="E38" s="2">
         <v>45689</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45598</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45507</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45416</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45325</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45227</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45136</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45045</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44954</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44863</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44772</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44590</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44499</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44317</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44226</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44044</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43953</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2631,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2657,56 +2742,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>259000</v>
+      </c>
+      <c r="E41" s="3">
         <v>227600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>160300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>159300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>162500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>135500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>208100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>196000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>192100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>200700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>447000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>826100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>859800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>921200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>267500</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2725,44 +2811,47 @@
       <c r="X41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>439100</v>
+      </c>
+      <c r="E42" s="3">
         <v>467200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>511600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>513400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>431900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>412100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>451700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>528800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>533900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>489200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>291800</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>16</v>
       </c>
@@ -2778,8 +2867,8 @@
       <c r="S42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -2793,56 +2882,59 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>222900</v>
+      </c>
+      <c r="E43" s="3">
         <v>240200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>184300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>183600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>148800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>166700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>119500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>118600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>105200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>122900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>90800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>77400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>84900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>82000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>59400</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2861,56 +2953,59 @@
       <c r="X43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E44" s="3">
         <v>38900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>39400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>38600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>30500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>22200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>27100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>21800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>32400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>40600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>44500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>39100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>42000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>33100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>22300</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>16</v>
       </c>
@@ -2929,56 +3024,59 @@
       <c r="X44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>123300</v>
+      </c>
+      <c r="E45" s="3">
         <v>119300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>115100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>111300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>107800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>104000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>99200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>94100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>86300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>104200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>88900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>93400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>81900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>63900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>56800</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2997,56 +3095,59 @@
       <c r="X45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1132900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1145200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1039400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1039600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>923700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>887000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>940900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>978000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>970600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>957500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>963000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1036000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1068600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1100200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>406000</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3065,44 +3166,47 @@
       <c r="X46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>325100</v>
+      </c>
+      <c r="E47" s="3">
         <v>282700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>241100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>207700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>250600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>276200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>189400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>109700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>87800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>113100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>63700</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3118,8 +3222,8 @@
       <c r="S47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -3133,56 +3237,59 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>129900</v>
+      </c>
+      <c r="E48" s="3">
         <v>123000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>125600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>130200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>133300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>136900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>129100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>139900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>146500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>171900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>175900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>180100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>179200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>171200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>168800</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3201,8 +3308,11 @@
       <c r="X48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3222,17 +3332,17 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>13000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9600</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
@@ -3269,8 +3379,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3337,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3405,56 +3521,59 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E52" s="3">
         <v>21200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>26900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>26100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>26400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>37800</v>
-      </c>
-      <c r="J52" s="3">
-        <v>40100</v>
       </c>
       <c r="K52" s="3">
         <v>40100</v>
       </c>
       <c r="L52" s="3">
+        <v>40100</v>
+      </c>
+      <c r="M52" s="3">
         <v>374500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>347400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>312900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>297100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>296600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>264700</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3473,8 +3592,11 @@
       <c r="X52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3541,56 +3663,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2073600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2024300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1863900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1826100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1749400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1734800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1686400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1642600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1598500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1617000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1550000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1529000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1545000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1567900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>839500</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3609,8 +3734,11 @@
       <c r="X54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3635,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3661,56 +3790,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E57" s="3">
         <v>64000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>31500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>47300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>41200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>46300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>38300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>34700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>29200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>30100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>43400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>20400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>40800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>54700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>42300</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3729,38 +3859,41 @@
       <c r="X57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E58" s="3">
         <v>15700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>18000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>20000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>20500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>16500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10200</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3797,56 +3930,59 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>576500</v>
+      </c>
+      <c r="E59" s="3">
         <v>563300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>505600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>485900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>447000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>426400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>367400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>348800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>319100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>412000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>334500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>321400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>311500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>283600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>242100</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3865,56 +4001,59 @@
       <c r="X59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>741200</v>
+      </c>
+      <c r="E60" s="3">
         <v>761300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>654100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>647200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>601300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>591800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>506500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>479300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>440900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>442200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>377800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>341800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>352300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>338300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>284400</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3933,38 +4072,41 @@
       <c r="X60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E61" s="3">
         <v>64600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>68000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>68300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>73600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>78800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>83300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>89400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>95200</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4001,56 +4143,59 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E62" s="3">
         <v>6600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9900</v>
-      </c>
-      <c r="I62" s="3">
-        <v>9300</v>
       </c>
       <c r="J62" s="3">
         <v>9300</v>
       </c>
       <c r="K62" s="3">
+        <v>9300</v>
+      </c>
+      <c r="L62" s="3">
         <v>9100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>236800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>232400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>234100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>230300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>240700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>235300</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4069,8 +4214,11 @@
       <c r="X62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4137,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4205,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4273,56 +4427,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>946000</v>
+      </c>
+      <c r="E66" s="3">
         <v>955100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>864700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>861500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>825500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>819700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>735400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>706300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>676000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>679000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>610200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>575900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>582500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>579000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>519700</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4341,8 +4498,11 @@
       <c r="X66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4367,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4435,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4503,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4548,11 +4715,11 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>949100</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4571,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4639,56 +4809,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1632100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1610000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1598800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1561000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1511400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1455100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1341700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1296200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1236200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1168400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1114800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1056200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-991900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-921000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-668200</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4707,8 +4880,11 @@
       <c r="X72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4775,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4843,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4911,56 +5093,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1127600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1069200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>999100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>964700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>923900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>915100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>950900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>936400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>922600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>938000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>939800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>953100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>962400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>988900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-629200</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4979,8 +5164,11 @@
       <c r="X76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5047,149 +5235,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45780</v>
+      </c>
+      <c r="E80" s="2">
         <v>45689</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45598</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45507</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45416</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45325</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45227</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45136</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45045</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44954</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44863</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44772</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44590</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44499</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44317</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44226</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44044</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43953</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-37800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-49600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-56300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-113400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-45500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-60000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-67900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-53600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-58600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-64300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-71000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-252800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-32400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-31400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-38400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-36200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-54300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-56000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-63700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5214,53 +5411,54 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E83" s="3">
         <v>-100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3500</v>
-      </c>
-      <c r="H83" s="3">
-        <v>2400</v>
       </c>
       <c r="I83" s="3">
         <v>2400</v>
       </c>
       <c r="J83" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K83" s="3">
         <v>1600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2200</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5276,14 +5474,17 @@
       <c r="V83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5350,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5418,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5486,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5554,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5622,53 +5835,56 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>52600</v>
+      </c>
+      <c r="E89" s="3">
         <v>53900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>36000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>18100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>23700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-41900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-12900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-37000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-48800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-48300</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5684,14 +5900,17 @@
       <c r="V89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
+      <c r="W89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5716,58 +5935,59 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>16</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>16</v>
@@ -5778,14 +5998,17 @@
       <c r="V91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5852,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5920,53 +6146,56 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E94" s="3">
         <v>500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-33900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-36300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-42600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-16900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-17700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-249300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-365600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5982,14 +6211,17 @@
       <c r="V94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6014,8 +6246,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6043,8 +6276,8 @@
       <c r="K96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6082,8 +6315,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6150,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6218,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6286,53 +6528,56 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E100" s="3">
         <v>11500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>15700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>9000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>12500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>9700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>703000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6348,49 +6593,52 @@
       <c r="V100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-200</v>
       </c>
       <c r="K101" s="3">
         <v>-200</v>
       </c>
       <c r="L101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M101" s="3">
         <v>600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-200</v>
       </c>
       <c r="O101" s="3">
         <v>-200</v>
@@ -6398,8 +6646,8 @@
       <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>16</v>
+      <c r="Q101" s="3">
+        <v>-200</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>16</v>
@@ -6416,59 +6664,62 @@
       <c r="V101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E102" s="3">
         <v>65200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>26900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-75000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-246400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-379100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-33700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-61400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>645100</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6484,10 +6735,13 @@
       <c r="V102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
+      <c r="W102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>IOT</t>
   </si>
@@ -656,337 +656,362 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="12" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45962</v>
+      </c>
+      <c r="F7" s="2">
         <v>45871</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45780</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45689</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45598</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45507</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45416</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45325</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45227</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45136</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45045</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44954</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44863</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44772</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44590</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44499</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44317</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44226</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44135</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44044</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43953</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>444300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>416000</v>
+      </c>
+      <c r="F8" s="3">
         <v>391500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>366900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>346300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>322000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>300200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>280700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>276300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>237500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>219300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>204300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>186600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>169800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>153500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>142600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>125800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>113800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>101000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>87700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>75900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>66200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>56800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>51000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>104900</v>
+      </c>
+      <c r="E9" s="3">
+        <v>96800</v>
+      </c>
+      <c r="F9" s="3">
         <v>90200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>82800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>79300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>75700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>73200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>68200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>68200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>61400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>58600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>57600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>51500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>47300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>44300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>39600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>38700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>31800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>28400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>25600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>21200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>18700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>18900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>16600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>339400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>319200</v>
+      </c>
+      <c r="F10" s="3">
         <v>301300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>284100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>267000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>246300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>227000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>212500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>208100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>176100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>160600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>146800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>135100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>122500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>109200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>103000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>87100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>82000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>72600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>62100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>54700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>47500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>37900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>34400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1013,82 +1038,90 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>89500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>86200</v>
+      </c>
+      <c r="F12" s="3">
         <v>85600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>83200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>73300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>77000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>76500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>73000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>73400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>60800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>64000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>60400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>54600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>50000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>41800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>41000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>126500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>29700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>25500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>23500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>20200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>33500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>21900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>24200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1161,8 +1194,14 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1172,54 +1211,54 @@
       <c r="E14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="3">
         <v>1300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>3600</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="3">
         <v>68700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>4800</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>1100</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>1500</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
@@ -1227,55 +1266,61 @@
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>6800</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F15" s="3">
         <v>2100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>2100</v>
       </c>
-      <c r="F15" s="3">
-        <v>4800</v>
-      </c>
-      <c r="G15" s="3">
-        <v>6800</v>
-      </c>
       <c r="H15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="J15" s="3">
         <v>2500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>2600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>3300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>3600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>3700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>3500</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1309,8 +1354,14 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1334,156 +1385,170 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>435300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>417700</v>
+      </c>
+      <c r="F17" s="3">
         <v>418100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>400100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>363400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>365700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>358400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>346700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>330600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>287500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>289000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>280100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>246600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>233300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>219300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>212900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>377500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>146100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>132300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>126300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>111200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>120500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>112900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>114700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>109900</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-26600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-33300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-17100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-43800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-58200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-66000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-54300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-50000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-69800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-75800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-60000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-63500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-65800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-70300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-251700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-32300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-31300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-38600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-35300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-54300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-56100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-63700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-68300</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1510,156 +1575,170 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>16</v>
+      <c r="D20" s="3">
+        <v>-7100</v>
       </c>
       <c r="E20" s="3">
+        <v>800</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1500</v>
       </c>
-      <c r="F20" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>16</v>
+      <c r="H20" s="3">
+        <v>800</v>
       </c>
       <c r="I20" s="3">
+        <v>600</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P20" s="3">
         <v>8500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>5600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>1600</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-800</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-24500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-29600</v>
       </c>
-      <c r="F21" s="3">
-        <v>-15100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-37000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="J21" s="3">
         <v>-55700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-63800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-51200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-46400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-66000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-72300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-48000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-54500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-61600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-67900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-249800</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X21" s="3">
         <v>-25400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-46000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1693,11 +1772,11 @@
       <c r="M22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1732,142 +1811,154 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-15200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-20500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-8600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-37300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-48600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-55900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-111500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-45400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-59500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-66900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-51500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-57900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-64200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-70300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-252000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-32400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-31000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-38400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-36200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-54300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-56000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-63600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F24" s="3">
         <v>1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>1600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>2600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>2100</v>
-      </c>
-      <c r="O24" s="3">
-        <v>700</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
       </c>
       <c r="Q24" s="3">
         <v>700</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>700</v>
+      </c>
+      <c r="T24" s="3">
         <v>800</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
@@ -1878,10 +1969,16 @@
         <v>0</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1954,156 +2051,174 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-16800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-22100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-11200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-37800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-49600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-56300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-113400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-45500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-60000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-67900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-53600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-58600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-64300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-71000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-252800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-32400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-31400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-38400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-36200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-54300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-56000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-63700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-16800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-22100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-11200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-37800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-49600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-56300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-113400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-45500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-60000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-67900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-53600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-58600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-64300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-71000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-252800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-32400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-31400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-38400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-36200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-54300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-56000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-63700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2176,8 +2291,14 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2250,8 +2371,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2324,8 +2451,14 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2398,156 +2531,174 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>16</v>
+      <c r="D32" s="3">
+        <v>7100</v>
       </c>
       <c r="E32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="3">
         <v>1500</v>
       </c>
-      <c r="F32" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>16</v>
+      <c r="H32" s="3">
+        <v>-800</v>
       </c>
       <c r="I32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P32" s="3">
         <v>-8500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-5600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>800</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-16800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-22100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-11200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-37800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-49600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-56300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-113400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-45500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-60000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-67900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-53600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-58600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-64300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-71000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-252800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-32400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-31400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-38400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-36200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-54300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-56000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-63700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2620,161 +2771,179 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-16800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-22100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-11200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-37800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-49600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-56300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-113400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-45500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-60000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-67900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-53600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-58600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-64300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-71000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-252800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-32400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-31400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-38400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-36200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-54300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-56000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-63700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45962</v>
+      </c>
+      <c r="F38" s="2">
         <v>45871</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45780</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45689</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45598</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45507</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45416</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45325</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45227</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45136</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45045</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44954</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44863</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44772</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44590</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44499</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44317</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44226</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44135</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44044</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43953</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2801,8 +2970,10 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2829,65 +3000,67 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>318800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>275100</v>
+      </c>
+      <c r="F41" s="3">
         <v>258500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>259000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>227600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>160300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>159300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>162500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>135500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>208100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>196000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>192100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>200700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>447000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>826100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>859800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>921200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>267500</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2903,53 +3076,59 @@
       <c r="Z41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>515000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>486700</v>
+      </c>
+      <c r="F42" s="3">
         <v>443300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>439100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>467200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>511600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>513400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>431900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>412100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>451700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>528800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>533900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>489200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>291800</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>16</v>
       </c>
@@ -2962,11 +3141,11 @@
       <c r="U42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
-      </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -2977,65 +3156,71 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>327900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>262900</v>
+      </c>
+      <c r="F43" s="3">
         <v>253000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>222900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>240200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>184300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>183600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>148800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>166700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>119500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>118600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>105200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>122900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>90800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>77400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>84900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>82000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>59400</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3051,65 +3236,71 @@
       <c r="Z43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>55000</v>
+      </c>
+      <c r="F44" s="3">
         <v>47600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>37900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>38900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>39400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>38600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>30500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>22200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>27100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>21800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>32400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>40600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>44500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>39100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>42000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>33100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>22300</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3125,65 +3316,71 @@
       <c r="Z44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>228400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>132000</v>
+      </c>
+      <c r="F45" s="3">
         <v>126700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>123300</v>
       </c>
-      <c r="F45" s="3">
-        <v>119300</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
+        <v>186400</v>
+      </c>
+      <c r="I45" s="3">
         <v>115100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>111300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>107800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>104000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>99200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>94100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>86300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>104200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>88900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>93400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>81900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>63900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>56800</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3199,65 +3396,71 @@
       <c r="Z45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1507100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1258000</v>
+      </c>
+      <c r="F46" s="3">
         <v>1186000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1132900</v>
       </c>
-      <c r="F46" s="3">
-        <v>1145200</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
+        <v>1212300</v>
+      </c>
+      <c r="I46" s="3">
         <v>1039400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1039600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>923700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>887000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>940900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>978000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>970600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>957500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>963000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1036000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1068600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1100200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>406000</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3273,53 +3476,59 @@
       <c r="Z46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>403100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>385300</v>
+      </c>
+      <c r="F47" s="3">
         <v>386300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>325100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>282700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>241100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>207700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>250600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>276200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>189400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>109700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>87800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>113100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>63700</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3332,11 +3541,11 @@
       <c r="U47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
-      </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -3347,65 +3556,71 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>141900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>140700</v>
+      </c>
+      <c r="F48" s="3">
         <v>134400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>129900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>123000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>125600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>130200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>133300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>136900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>129100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>139900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>146500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>171900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>175900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>180100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>179200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>171200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>168800</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3421,8 +3636,14 @@
       <c r="Z48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3448,20 +3669,20 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>13000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>11200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>9600</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
       <c r="P49" s="3">
         <v>0</v>
       </c>
@@ -3495,8 +3716,14 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3569,8 +3796,14 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3643,65 +3876,71 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>29100</v>
+      </c>
+      <c r="F52" s="3">
         <v>26400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>25100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>21200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>26900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>25800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>26100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>26400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>37800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>40100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>40100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>374500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>347400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>312900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>297100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>296600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>264700</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3717,8 +3956,14 @@
       <c r="Z52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3791,65 +4036,71 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2540700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2313700</v>
+      </c>
+      <c r="F54" s="3">
         <v>2207100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2073600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2024300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1863900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1826100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1749400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1734800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1686400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1642600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1598500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1617000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1550000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1529000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1545000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1567900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>839500</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3865,8 +4116,14 @@
       <c r="Z54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3893,8 +4150,10 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3921,65 +4180,67 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>47700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>19800</v>
+      </c>
+      <c r="F57" s="3">
         <v>30100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>22300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>64000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>31500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>47300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>41200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>46300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>38300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>34700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>29200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>30100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>43400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>20400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>40800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>54700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>42300</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3995,47 +4256,53 @@
       <c r="Z57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E58" s="3">
         <v>12800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
+        <v>12800</v>
+      </c>
+      <c r="G58" s="3">
         <v>14200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>15700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>18000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>19400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>20000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>20700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>20500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>16500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>10200</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4069,65 +4336,71 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>679300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>620900</v>
+      </c>
+      <c r="F59" s="3">
         <v>611300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>576500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>563300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>505600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>485900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>447000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>426400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>367400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>348800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>319100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>412000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>334500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>321400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>311500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>283600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>242100</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4143,65 +4416,71 @@
       <c r="Z59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>917000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>806400</v>
+      </c>
+      <c r="F60" s="3">
         <v>791600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>741200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>761300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>654100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>647200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>601300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>591800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>506500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>479300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>440900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>442200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>377800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>341800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>352300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>338300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>284400</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4217,47 +4496,53 @@
       <c r="Z60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>62800</v>
+      </c>
+      <c r="F61" s="3">
         <v>64400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>67900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>64600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>68000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>68300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>73600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>78800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>83300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>89400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>95200</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4291,65 +4576,71 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F62" s="3">
         <v>7200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>7400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>6600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>8500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>9200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>9600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>9900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>9300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>9300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>9100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>236800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>232400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>234100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>230300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>240700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>235300</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4365,8 +4656,14 @@
       <c r="Z62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4439,8 +4736,14 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4513,8 +4816,14 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4587,65 +4896,71 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1120200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1010300</v>
+      </c>
+      <c r="F66" s="3">
         <v>992300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>946000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>955100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>864700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>861500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>825500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>819700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>735400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>706300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>676000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>679000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>610200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>575900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>582500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>579000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>519700</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4661,8 +4976,14 @@
       <c r="Z66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4689,8 +5010,10 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4763,8 +5086,14 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4837,8 +5166,14 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4888,14 +5223,14 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>949100</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4911,8 +5246,14 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4985,65 +5326,71 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1619100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1641200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1648900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-1632100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-1610000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-1598800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-1561000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-1511400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-1455100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-1341700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-1296200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-1236200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-1168400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-1114800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-1056200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-991900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-921000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-668200</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5059,8 +5406,14 @@
       <c r="Z72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5133,8 +5486,14 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5207,8 +5566,14 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5281,65 +5646,71 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1420400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1303400</v>
+      </c>
+      <c r="F76" s="3">
         <v>1214800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1127600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1069200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>999100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>964700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>923900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>915100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>950900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>936400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>922600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>938000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>939800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>953100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>962400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>988900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-629200</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5355,8 +5726,14 @@
       <c r="Z76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5429,161 +5806,179 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45962</v>
+      </c>
+      <c r="F80" s="2">
         <v>45871</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45780</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45689</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45598</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45507</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45416</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45325</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45227</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45136</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45045</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44954</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44863</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44772</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44590</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44499</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44317</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44226</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44135</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44044</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43953</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-16800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-22100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-11200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-37800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-49600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-56300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-113400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-45500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-60000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-67900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-53600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-58600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-64300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-71000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-252800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-32400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-31400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-38400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-36200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-54300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-56000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-63700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5610,62 +6005,64 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F83" s="3">
         <v>2500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>2600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>-100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>3600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>3700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>3500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>2400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>2400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>3400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>3300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>2600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>2400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>2200</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5678,14 +6075,20 @@
       <c r="X83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5758,8 +6161,14 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5832,8 +6241,14 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5906,8 +6321,14 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5980,8 +6401,14 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6054,62 +6481,68 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>69700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>63700</v>
+      </c>
+      <c r="F89" s="3">
         <v>50200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>52600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>53900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>36000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>18100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>23700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-41900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>11900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>7700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>10500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-4400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-12900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-48800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-48300</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6122,14 +6555,20 @@
       <c r="X89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6156,67 +6595,69 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-6000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-6900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-5300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-4800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-5000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-5100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-3400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-3000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-2500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-6000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-10300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-10700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-9400</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>16</v>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>16</v>
@@ -6224,14 +6665,20 @@
       <c r="X91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6304,8 +6751,14 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6378,62 +6831,68 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-54800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-68200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-18300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-33900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-36300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>3100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-42600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-16900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-17700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-249300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-365600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-10700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-9500</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6446,14 +6905,20 @@
       <c r="X94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6480,8 +6945,10 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6515,11 +6982,11 @@
       <c r="M96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6554,8 +7021,14 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6628,8 +7101,14 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6702,8 +7181,14 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6776,62 +7261,68 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F100" s="3">
         <v>18400</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-400</v>
-      </c>
-      <c r="F100" s="3">
-        <v>11500</v>
       </c>
       <c r="G100" s="3">
         <v>-400</v>
       </c>
       <c r="H100" s="3">
+        <v>11500</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J100" s="3">
         <v>15700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>9000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>12500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>6700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>9700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-1700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>703000</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6844,67 +7335,73 @@
       <c r="X100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>100</v>
+      </c>
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-200</v>
       </c>
       <c r="R101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>16</v>
+      <c r="S101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T101" s="3">
+        <v>-200</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>16</v>
@@ -6918,68 +7415,74 @@
       <c r="X101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>14900</v>
+      </c>
+      <c r="F102" s="3">
         <v>600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>35100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>65200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-3000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>26900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-75000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>9700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>3800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-7400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-246400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-379100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-33700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-61400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>645100</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6992,10 +7495,16 @@
       <c r="X102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>0</v>
       </c>
     </row>
